--- a/results/Int Task Remove ACC -0.3/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_8_permute.xlsx
@@ -440,687 +440,687 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5856109981145241</v>
+        <v>0.5814948706147839</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5849633297207417</v>
+        <v>0.5752882031563163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5849633297207417</v>
+        <v>0.5759358715500987</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6085883798268925</v>
+        <v>0.5759358715500987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6130923660495569</v>
+        <v>0.5839138842288106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6130923660495569</v>
+        <v>0.5797188859361313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.59954421960598</v>
+        <v>0.5803665543299137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6008590421188593</v>
+        <v>0.5515545897234141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5981505263001619</v>
+        <v>0.5489639161482845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5916051783778968</v>
+        <v>0.5492283652775509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.602905043276868</v>
+        <v>0.5034248481969209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6164717475540775</v>
+        <v>0.4964526701011031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6159614071291775</v>
+        <v>0.4899268079041525</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6200831019790074</v>
+        <v>0.5001326885104741</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6035378654037442</v>
+        <v>0.5075316967798447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5940631634425524</v>
+        <v>0.5227324183084163</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5940631634425524</v>
+        <v>0.519970084772184</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5879103137016197</v>
+        <v>0.5207699274017548</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5876208114969491</v>
+        <v>0.5193372626453079</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5843629838027229</v>
+        <v>0.5173979690306872</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5807664756446991</v>
+        <v>0.5173979690306872</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5814187834968897</v>
+        <v>0.5292916846059059</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5806040946004127</v>
+        <v>0.5269849458853572</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5799907581988509</v>
+        <v>0.5204099054292798</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.591035452885372</v>
+        <v>0.5232705954837656</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5857167777662307</v>
+        <v>0.5208126104191101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5817472571521891</v>
+        <v>0.5240453850379322</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5711293926392209</v>
+        <v>0.5218917484448535</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.562459172766008</v>
+        <v>0.5222499146339653</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5384462639369331</v>
+        <v>0.518672892201256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.524393344418546</v>
+        <v>0.5198012084861262</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5256200172216696</v>
+        <v>0.5210919058152828</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5243590124263253</v>
+        <v>0.5339079457220481</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.509550789079086</v>
+        <v>0.5737748118235669</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4965927817450302</v>
+        <v>0.5751499472957525</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5037022878097303</v>
+        <v>0.5678140356607331</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5037022878097303</v>
+        <v>0.5642713452202444</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5324984782576421</v>
+        <v>0.5763998173909171</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5398288225425717</v>
+        <v>0.580256135219799</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5407316611488042</v>
+        <v>0.5999218715204062</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5477576569621569</v>
+        <v>0.5976012144246329</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.539013205754413</v>
+        <v>0.5436675104295026</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5310500393426073</v>
+        <v>0.5308755957064596</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.52885186394881</v>
+        <v>0.5258018839912704</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5366582166664192</v>
+        <v>0.5099191620766959</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.513611243077928</v>
+        <v>0.5171808423771842</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5157602402125986</v>
+        <v>0.5248108956752824</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5160840744094898</v>
+        <v>0.5148406995560966</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.514975243849934</v>
+        <v>0.5094524325608326</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5178062413706074</v>
+        <v>0.5328668512552519</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5333688406550172</v>
+        <v>0.5328668512552519</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5228929435693395</v>
+        <v>0.5547456092165626</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.511067891978562</v>
+        <v>0.5753837759995249</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5369300889291387</v>
+        <v>0.5260969535460309</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5369987529135799</v>
+        <v>0.5303364906394288</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5266898763305967</v>
+        <v>0.5520036892973262</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5128782086494351</v>
+        <v>0.5596393099455141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5122305402556527</v>
+        <v>0.5549636637617471</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5198355404783467</v>
+        <v>0.5466952209866829</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5217052422168446</v>
+        <v>0.5474115533649064</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4946581275888178</v>
+        <v>0.5378097302433302</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4966549504876999</v>
+        <v>0.5378097302433302</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4999962884332734</v>
+        <v>0.5694387739952789</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5007274670784031</v>
+        <v>0.5343681799961399</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5089996214201938</v>
+        <v>0.5247320248823434</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5089996214201938</v>
+        <v>0.545520510117731</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.508131114806182</v>
+        <v>0.5300599789183009</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4894619341716526</v>
+        <v>0.5345982971331859</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4894619341716526</v>
+        <v>0.5311483958608608</v>
       </c>
     </row>
     <row r="71">
@@ -1130,197 +1130,197 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4946182282465074</v>
+        <v>0.5433093442403907</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4946182282465074</v>
+        <v>0.5358917781373873</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.492405206585804</v>
+        <v>0.5404746351529908</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4931215389640275</v>
+        <v>0.5390531050967234</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4790500616120076</v>
+        <v>0.5357451712516887</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4864685556066927</v>
+        <v>0.5261173671630268</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4906487076324658</v>
+        <v>0.5261173671630268</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4945003860029396</v>
+        <v>0.5277151966388052</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4965807191531689</v>
+        <v>0.531822045221729</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4971940555547307</v>
+        <v>0.5147469824962513</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4958449010496311</v>
+        <v>0.517901814213816</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4958940793087578</v>
+        <v>0.5002774396128093</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4969342458838725</v>
+        <v>0.5031771011179239</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4916842347491723</v>
+        <v>0.5031771011179239</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4826122377778108</v>
+        <v>0.5036076428582033</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4872043737102306</v>
+        <v>0.5039806553142212</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4943138797749306</v>
+        <v>0.5030583309826744</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4963301883991271</v>
+        <v>0.5030137921819559</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4994015098653444</v>
+        <v>0.5027688287780038</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5011580088186826</v>
+        <v>0.5031808126846504</v>
       </c>
     </row>
   </sheetData>
